--- a/artfynd/A 54924-2022 artfynd.xlsx
+++ b/artfynd/A 54924-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54924-2022 artfynd.xlsx
+++ b/artfynd/A 54924-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105400555</v>
+        <v>105400463</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591074.3762744373</v>
+        <v>591085</v>
       </c>
       <c r="R2" t="n">
-        <v>6326488.183417798</v>
+        <v>6326466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -807,12 +802,7 @@
         <v>105400484</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591142.2389883631</v>
+        <v>591142</v>
       </c>
       <c r="R3" t="n">
-        <v>6326227.039778426</v>
+        <v>6326227</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -933,15 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105400542</v>
+        <v>105400499</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -989,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591037.240886596</v>
+        <v>591066</v>
       </c>
       <c r="R4" t="n">
-        <v>6326640.699806951</v>
+        <v>6326364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1065,12 +1050,7 @@
         <v>105400510</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591047.8113527785</v>
+        <v>591048</v>
       </c>
       <c r="R5" t="n">
-        <v>6326432.68000517</v>
+        <v>6326433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1191,15 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105400463</v>
+        <v>105400527</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1201,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591085.2135643604</v>
+        <v>590992</v>
       </c>
       <c r="R6" t="n">
-        <v>6326466.128314186</v>
+        <v>6326648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,15 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105400527</v>
+        <v>105400542</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1325,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1376,10 +1346,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590992.4088782448</v>
+        <v>591038</v>
       </c>
       <c r="R7" t="n">
-        <v>6326647.869440479</v>
+        <v>6326640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,12 +1422,7 @@
         <v>105400550</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591023.7327628842</v>
+        <v>591023</v>
       </c>
       <c r="R8" t="n">
-        <v>6326536.549580351</v>
+        <v>6326536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1578,15 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105400499</v>
+        <v>105400555</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1573,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1634,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591066.7568488166</v>
+        <v>591074</v>
       </c>
       <c r="R9" t="n">
-        <v>6326364.039659536</v>
+        <v>6326488</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 54924-2022 artfynd.xlsx
+++ b/artfynd/A 54924-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400463</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400484</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1168,6 +1188,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400527</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1416,6 +1446,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400542</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1540,6 +1575,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400550</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1664,8 +1704,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105400555</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>